--- a/docs/oc-regiones/gas-licuado-de-petroleo/coquimbo.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M344"/>
+  <dimension ref="A1:M347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4731.02</v>
+        <v>4690.95</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2635</v>
+        <v>2621.46</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1230.06</v>
+        <v>1217.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>508.53</v>
+        <v>503.45</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>373.39</v>
+        <v>369.67</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>170.32</v>
+        <v>168.53</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>690.58</v>
+        <v>686.8</v>
       </c>
     </row>
     <row r="9">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>363.7</v>
+        <v>361.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3511-636-CM25</t>
+          <t>2125-4276-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>250.14</v>
+        <v>5007.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2125-4276-CM25</t>
+          <t>3511-636-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5064.22</v>
+        <v>247.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1430710-7225-CM25</t>
+          <t>2555-231-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>153.14</v>
+        <v>1821.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1343-331-CM25</t>
+          <t>2555-229-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.511.042-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18.8</v>
+        <v>137.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2555-229-CM25</t>
+          <t>1343-331-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.042-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>138.12</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2555-231-CM25</t>
+          <t>1430710-7225-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1831.4</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1419.3</v>
+        <v>1417.5</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>552.46</v>
+        <v>551.76</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>81.72</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1163.64</v>
+        <v>1162.16</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>817.24</v>
+        <v>820.16</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>284.61</v>
+        <v>287.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>136.21</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1159-255-CM25</t>
+          <t>548238-261-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>62.18</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1574-412-CM25</t>
+          <t>548238-260-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>115.1</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>548238-260-CM25</t>
+          <t>1159-255-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>119.7</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>548238-261-CM25</t>
+          <t>1574-412-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>276.23</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>88.39</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>409.56</v>
+        <v>412.52</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>226.38</v>
+        <v>228.01</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1556.34</v>
+        <v>1553.58</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>306.06</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>543.3</v>
+        <v>542.34</v>
       </c>
     </row>
     <row r="33">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4527.53</v>
+        <v>4520.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079505-1228-CM25</t>
+          <t>1461054-573-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>557.99</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1461054-573-CM25</t>
+          <t>1962-760-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>158.46</v>
+        <v>763.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1962-760-CM25</t>
+          <t>1079505-1228-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>759.3200000000001</v>
+        <v>560.87</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>375.03</v>
+        <v>377.68</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>151.96</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>126.4</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>70.34</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>369.93</v>
+        <v>368.6</v>
       </c>
     </row>
     <row r="42">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>366.81</v>
+        <v>365.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>548238-280-CM25</t>
+          <t>2125-4516-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>587.62</v>
+        <v>3660.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2125-4516-CM25</t>
+          <t>548238-280-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3668.08</v>
+        <v>586.35</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>827.0700000000001</v>
+        <v>823.6</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1192.13</v>
+        <v>1191.17</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>268.87</v>
+        <v>269.9</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1091.07</v>
+        <v>1095.26</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>761.8</v>
+        <v>764.73</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2387.14</v>
+        <v>2396.3</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>783.84</v>
+        <v>787.4</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>86.38</v>
+        <v>86.26000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>454.61</v>
+        <v>453.98</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4585.1</v>
+        <v>4590.98</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>67.61</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>991.58</v>
+        <v>1003.76</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>688.54</v>
+        <v>697.39</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>404.48</v>
+        <v>409.67</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>265.75</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>310.05</v>
+        <v>314.03</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>310.05</v>
+        <v>314.03</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>111.23</v>
+        <v>111.84</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>120.15</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>331.71</v>
+        <v>326.95</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>379.09</v>
+        <v>373.66</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>132.68</v>
+        <v>130.78</v>
       </c>
     </row>
     <row r="67">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>180.07</v>
+        <v>177.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1079505-4-CM26</t>
+          <t>1079505-6-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>189.55</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1079505-6-CM26</t>
+          <t>1079505-5-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>126.05</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1079505-5-CM26</t>
+          <t>1079505-4-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>110.88</v>
+        <v>186.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1079505-8-CM26</t>
+          <t>1079505-2-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>118.47</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1079505-2-CM26</t>
+          <t>1079505-8-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>118.47</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>288.36</v>
+        <v>284.7</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4805.96</v>
+        <v>4736.7</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1583.77</v>
+        <v>1563.3</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5256.93</v>
+        <v>5246.58</v>
       </c>
     </row>
     <row r="77">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7303.05</v>
+        <v>7288.67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057440-10-CM26</t>
+          <t>1962-17-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1194.76</v>
+        <v>848.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1962-17-CM26</t>
+          <t>1057440-10-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>848.11</v>
+        <v>1194.77</v>
       </c>
     </row>
     <row r="80">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>376.94</v>
+        <v>375.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1079505-19-CM26</t>
+          <t>1079505-16-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>435.31</v>
+        <v>165.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1079505-16-CM26</t>
+          <t>1079505-17-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>166.71</v>
+        <v>138.19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1079505-17-CM26</t>
+          <t>1079505-18-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>138.93</v>
+        <v>253.36</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1079505-18-CM26</t>
+          <t>1079505-19-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>254.7</v>
+        <v>433.01</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>69.45999999999999</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>138.93</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="87">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>469.83</v>
+        <v>476.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1346282-31-CM26</t>
+          <t>1002588-19-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>70.47</v>
+        <v>131.55</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1002588-19-CM26</t>
+          <t>1346282-31-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>128.43</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>120.4</v>
+        <v>124.06</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>64.61</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>208.39</v>
+        <v>214.59</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1424.65</v>
+        <v>1419.58</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>690.89</v>
+        <v>688.4299999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>837.4</v>
+        <v>834.42</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>243.04</v>
+        <v>242.18</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>288.43</v>
+        <v>289.26</v>
       </c>
     </row>
     <row r="98">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1967.8</v>
+        <v>1973.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2146-35-CM26</t>
+          <t>1079505-35-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>393.56</v>
+        <v>326.6</v>
       </c>
     </row>
     <row r="100">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>279.13</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1079505-35-CM26</t>
+          <t>2146-35-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>325.65</v>
+        <v>394.7</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>188.85</v>
+        <v>189.82</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>104524.14</v>
+        <v>104083.43</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3507.05</v>
+        <v>3538.95</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>79.42</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4652.21</v>
+        <v>4684.6</v>
       </c>
     </row>
     <row r="107">
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2062.43</v>
+        <v>2076.02</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2555-23-CM26</t>
+          <t>3000-187-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>137.91</v>
+        <v>260.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3000-187-CM26</t>
+          <t>2555-23-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>257.8</v>
+        <v>139.14</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5056.69</v>
+        <v>5048.03</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>156.21</v>
+        <v>156.05</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>316.96</v>
+        <v>314.69</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>212.46</v>
+        <v>210.93</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2001.34</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1156.15</v>
+        <v>1149.85</v>
       </c>
     </row>
     <row r="116">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>323.72</v>
+        <v>321.96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057439-1313-CM26</t>
+          <t>3593-49-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2824.51</v>
+        <v>1322.23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1962-79-CM26</t>
+          <t>1057439-1313-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>820</v>
+        <v>2807.87</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3593-49-CM26</t>
+          <t>1962-79-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1330.06</v>
+        <v>815.17</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3750-60-CM26</t>
+          <t>4036-128-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1503.34</v>
+        <v>451.08</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1657-38-CM26</t>
+          <t>3750-60-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2574.48</v>
+        <v>1494.21</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4036-128-CM26</t>
+          <t>1657-38-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7858,17 +7858,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>453.84</v>
+        <v>2558.84</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>69.37</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>259.34</v>
+        <v>258.34</v>
       </c>
     </row>
     <row r="125">
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>277.48</v>
+        <v>276.41</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3707-123-CM26</t>
+          <t>2448-148-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>328</v>
+        <v>632.65</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2448-148-CM26</t>
+          <t>707418-16-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8163,17 +8163,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>629.39</v>
+        <v>6060.79</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>707418-16-CM26</t>
+          <t>3707-123-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8224,17 +8224,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6029.58</v>
+        <v>329.7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1962-95-CM26</t>
+          <t>1797-10-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>463.84</v>
+        <v>232.14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1797-10-CM26</t>
+          <t>1962-95-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>231.92</v>
+        <v>464.29</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1079505-59-CM26</t>
+          <t>3182-22-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.102.073-2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>77.69</v>
+        <v>1120.21</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3182-22-CM26</t>
+          <t>1079505-59-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.102.073-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1072.83</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>966.76</v>
+        <v>994.84</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>683.87</v>
+        <v>686.5599999999999</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>738.58</v>
+        <v>741.49</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>119.53</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1758.2</v>
+        <v>1787.18</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>107.98</v>
+        <v>108.24</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>373.02</v>
+        <v>373.94</v>
       </c>
     </row>
     <row r="140">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>109.86</v>
+        <v>110.13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1079505-68-CM26</t>
+          <t>707418-20-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>259.74</v>
+        <v>108.49</v>
       </c>
     </row>
     <row r="142">
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>238.09</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1079505-66-CM26</t>
+          <t>1079505-68-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>238.09</v>
+        <v>260.38</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>707418-20-CM26</t>
+          <t>1079505-66-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>108.22</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="145">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>79.23</v>
+        <v>78.20999999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3712-206-CM26</t>
+          <t>1079505-79-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1342.57</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3712-205-CM26</t>
+          <t>3532-43-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1618.18</v>
+        <v>545.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3511-61-CM26</t>
+          <t>1574-34-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9444,17 +9444,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>252.42</v>
+        <v>89.34</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3532-43-CM26</t>
+          <t>3712-205-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>549.87</v>
+        <v>1606.76</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1079505-79-CM26</t>
+          <t>3712-206-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>410.79</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1574-34-CM26</t>
+          <t>3511-61-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>89.98</v>
+        <v>250.64</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1962-120-CM26</t>
+          <t>1574-38-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>674.85</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1574-38-CM26</t>
+          <t>1962-120-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>687.08</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>733.3</v>
+        <v>744.78</v>
       </c>
     </row>
     <row r="155">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>315.53</v>
+        <v>315.51</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5135.91</v>
+        <v>5140.34</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>70.5</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3291.86</v>
+        <v>3282.78</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2553-2-CM26</t>
+          <t>3687-82-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10176,17 +10176,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>371.25</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2711-65-CM26</t>
+          <t>1430710-159-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>761.3</v>
+        <v>243.17</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1430710-159-CM26</t>
+          <t>3687-81-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10298,17 +10298,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>246.01</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3687-81-CM26</t>
+          <t>2711-65-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>752.52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3687-82-CM26</t>
+          <t>2553-2-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>366.97</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>273.62</v>
+        <v>272.05</v>
       </c>
     </row>
     <row r="166">
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>115.19</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1574-42-CM26</t>
+          <t>1574-41-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1189.78</v>
+        <v>6090.86</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1242121-152-CM26</t>
+          <t>1574-42-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4642.85</v>
+        <v>1182.16</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1057440-161-CM26</t>
+          <t>1242121-152-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1160.71</v>
+        <v>4613.11</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1574-41-CM26</t>
+          <t>1057440-161-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6130.13</v>
+        <v>1153.28</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>32952.09</v>
+        <v>32810.13</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>73.23999999999999</v>
+        <v>72.92</v>
       </c>
     </row>
     <row r="173">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>557.14</v>
+        <v>554.74</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3511-76-CM26</t>
+          <t>1797-21-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11030,17 +11030,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>446.99</v>
+        <v>1065.69</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1346282-128-CM26</t>
+          <t>3511-76-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>69.64</v>
+        <v>440.52</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1797-21-CM26</t>
+          <t>1346282-128-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1081.34</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>366.2</v>
+        <v>358.32</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1054.57</v>
+        <v>1031.88</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>826.3</v>
+        <v>808.52</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>142.65</v>
+        <v>139.33</v>
       </c>
     </row>
     <row r="181">
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1396.78</v>
+        <v>1364.28</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3000-426-CM26</t>
+          <t>2147-183-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>149.17</v>
+        <v>1318.46</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2147-183-CM26</t>
+          <t>3000-426-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11579,17 +11579,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1344.99</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="184">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>349.09</v>
+        <v>339.75</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2992-89-CM26</t>
+          <t>1242121-175-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>169.85</v>
+        <v>274.45</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1242121-175-CM26</t>
+          <t>2992-89-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>273.31</v>
+        <v>170.56</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>962.0599999999999</v>
+        <v>970.23</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>410.35</v>
+        <v>409.67</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>676.3099999999999</v>
+        <v>684.63</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6297.99</v>
+        <v>6375.5</v>
       </c>
     </row>
     <row r="191">
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>118.84</v>
+        <v>120.31</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1229-14-CM26</t>
+          <t>1079505-142-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>60.804.006-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE COQUIMBO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12163,13 +12163,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>825.64</v>
+        <v>1160.33</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1079505-142-CM26</t>
+          <t>1242121-182-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1145.09</v>
+        <v>5801.67</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1242121-182-CM26</t>
+          <t>1229-14-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>60.804.006-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE COQUIMBO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12285,13 +12285,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5725.45</v>
+        <v>836.64</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1079505-157-CM26</t>
+          <t>3509-139-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12311,17 +12311,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>390.58</v>
+        <v>1942.82</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1079505-158-CM26</t>
+          <t>1057440-223-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>390.58</v>
+        <v>1495.7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1079505-159-CM26</t>
+          <t>1079505-158-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>92.06</v>
+        <v>397.96</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1057440-223-CM26</t>
+          <t>1079505-157-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12499,12 +12499,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12529,13 +12529,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1467.94</v>
+        <v>397.96</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3509-139-CM26</t>
+          <t>1079505-159-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12555,17 +12555,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12575,12 +12575,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1906.76</v>
+        <v>93.81</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>542.8099999999999</v>
+        <v>548.98</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>733.6799999999999</v>
+        <v>742.02</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1693.78</v>
+        <v>1709.04</v>
       </c>
     </row>
     <row r="203">
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4997.84</v>
+        <v>5013.56</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1346282-164-CM26</t>
+          <t>1886-10-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>83.3</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3712-325-CM26</t>
+          <t>3712-326-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4489.19</v>
+        <v>4471.58</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3712-326-CM26</t>
+          <t>1346282-164-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12982,17 +12982,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13017,13 +13017,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4453.13</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1886-10-CM26</t>
+          <t>3712-325-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13078,13 +13078,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>131.97</v>
+        <v>4507.79</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1962-211-CM26</t>
+          <t>3712-317-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>445.31</v>
+        <v>1113.2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>548238-54-CM26</t>
+          <t>1660-316-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13165,17 +13165,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13185,12 +13185,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>177.7</v>
+        <v>844.24</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3712-317-CM26</t>
+          <t>1962-211-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13261,13 +13261,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1110.9</v>
+        <v>446.24</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1660-316-CM26</t>
+          <t>548238-54-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13287,17 +13287,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>842.5</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="212">
@@ -13383,13 +13383,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>610.85</v>
+        <v>608.22</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1962-223-CM26</t>
+          <t>627786-81-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13444,13 +13444,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>932.77</v>
+        <v>2222.28</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>627786-81-CM26</t>
+          <t>3267-63-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13475,12 +13475,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13505,13 +13505,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2231.86</v>
+        <v>432.32</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3267-63-CM26</t>
+          <t>1962-223-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>434.19</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2195.36</v>
+        <v>2182.2</v>
       </c>
     </row>
     <row r="217">
@@ -13688,13 +13688,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>704.8099999999999</v>
+        <v>700.59</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1250339-12-CM26</t>
+          <t>2555-69-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13719,12 +13719,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coquimbo</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>220.75</v>
+        <v>168.77</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2555-69-CM26</t>
+          <t>1250339-12-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13780,12 +13780,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Dirección Regional de Gendarmeria - Coquimbo</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13795,12 +13795,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>170.22</v>
+        <v>218.86</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>340.44</v>
+        <v>342.27</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>272.83</v>
+        <v>274.3</v>
       </c>
     </row>
     <row r="222">
@@ -13993,13 +13993,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>372.26</v>
+        <v>376.42</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2146-203-CM26</t>
+          <t>1079505-204-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14024,12 +14024,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14039,12 +14039,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14054,13 +14054,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>522.52</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1079505-204-CM26</t>
+          <t>1079505-202-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14115,13 +14115,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>510.66</v>
+        <v>340.23</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1079505-202-CM26</t>
+          <t>2146-203-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14161,12 +14161,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14176,13 +14176,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>336.46</v>
+        <v>528.37</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1079505-195-CM26</t>
+          <t>1079505-200-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14237,13 +14237,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>109.35</v>
+        <v>396.93</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1079505-200-CM26</t>
+          <t>1079505-195-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>392.54</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>680.88</v>
+        <v>688.5</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>140.19</v>
+        <v>141.76</v>
       </c>
     </row>
     <row r="230">
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>93.06</v>
+        <v>93.77</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3750-123-CM26</t>
+          <t>1962-263-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14507,17 +14507,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1841.4</v>
+        <v>425.42</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1962-263-CM26</t>
+          <t>3750-123-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14568,17 +14568,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14588,12 +14588,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14603,13 +14603,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>423.82</v>
+        <v>1848.38</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1242121-249-CM26</t>
+          <t>3511-144-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14629,17 +14629,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14664,13 +14664,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6204.28</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1442-10-CM26</t>
+          <t>1242121-249-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14710,12 +14710,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14725,13 +14725,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>387.93</v>
+        <v>6188.62</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3511-144-CM26</t>
+          <t>1442-10-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>44.45</v>
+        <v>386.95</v>
       </c>
     </row>
     <row r="236">
@@ -14847,13 +14847,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>504.4</v>
+        <v>509.19</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1323-5-CM26</t>
+          <t>1057440-275-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14873,17 +14873,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>145.47</v>
+        <v>1583.46</v>
       </c>
     </row>
     <row r="238">
@@ -14969,13 +14969,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>110.48</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1057440-275-CM26</t>
+          <t>1323-5-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14995,17 +14995,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1571.75</v>
+        <v>146.56</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>168.23</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>631.13</v>
+        <v>629.5700000000001</v>
       </c>
     </row>
     <row r="242">
@@ -15213,13 +15213,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>964.74</v>
+        <v>962.36</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1057439-3641-CM26</t>
+          <t>1346282-230-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15259,12 +15259,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15274,13 +15274,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3405.58</v>
+        <v>1354.84</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1886-13-CM26</t>
+          <t>1962-277-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15320,12 +15320,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>72.36</v>
+        <v>1035.62</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1962-277-CM26</t>
+          <t>1886-13-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15396,13 +15396,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1032.19</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1346282-230-CM26</t>
+          <t>1057439-3641-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15442,12 +15442,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15457,13 +15457,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1350.36</v>
+        <v>3416.88</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1962-282-CM26</t>
+          <t>3260-66-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15483,17 +15483,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>241.38</v>
+        <v>603.78</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3260-66-CM26</t>
+          <t>1962-282-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15544,17 +15544,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>601.87</v>
+        <v>242.15</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1929.48</v>
+        <v>1939.74</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>180.56</v>
+        <v>181.52</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>730.2</v>
+        <v>734.08</v>
       </c>
     </row>
     <row r="252">
@@ -15823,13 +15823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2355.44</v>
+        <v>2367.97</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1346282-238-CM26</t>
+          <t>1660-423-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15869,12 +15869,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15884,13 +15884,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>90.69</v>
+        <v>2729.69</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1660-423-CM26</t>
+          <t>627786-105-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15945,13 +15945,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2691.18</v>
+        <v>489.55</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>627786-105-CM26</t>
+          <t>1242121-279-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15976,12 +15976,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -15991,12 +15991,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16006,13 +16006,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>482.65</v>
+        <v>6132.78</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1242121-279-CM26</t>
+          <t>1346282-238-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16037,12 +16037,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6046.26</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>550.46</v>
+        <v>556.92</v>
       </c>
     </row>
     <row r="258">
@@ -16189,13 +16189,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6046.26</v>
+        <v>6148.52</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1984-10-CM26</t>
+          <t>707418-78-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16220,12 +16220,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.701.009-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>154.89</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1079505-275-CM26</t>
+          <t>707418-74-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16296,12 +16296,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16311,13 +16311,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>215.29</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>707418-74-CM26</t>
+          <t>3511-220-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16337,17 +16337,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16372,13 +16372,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>120.93</v>
+        <v>157.62</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>707418-75-CM26</t>
+          <t>707418-77-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16418,12 +16418,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>98.53</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>707418-76-CM26</t>
+          <t>1079505-275-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16494,13 +16494,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>120.93</v>
+        <v>217.48</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>707418-77-CM26</t>
+          <t>707418-75-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>120.93</v>
+        <v>99.53</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>707418-78-CM26</t>
+          <t>707418-76-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16616,13 +16616,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>120.93</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3511-220-CM26</t>
+          <t>1984-10-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16642,17 +16642,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.701.009-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16662,12 +16662,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16677,13 +16677,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>156.03</v>
+        <v>156.46</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3000-652-CM26</t>
+          <t>1962-310-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>234.14</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="268">
@@ -16799,13 +16799,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>328.79</v>
+        <v>331.87</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1962-310-CM26</t>
+          <t>3000-652-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16825,17 +16825,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1016.67</v>
+        <v>236.34</v>
       </c>
     </row>
     <row r="270">
@@ -16921,13 +16921,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>219.38</v>
+        <v>217.72</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1079505-271-CM26</t>
+          <t>4036-271-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16947,17 +16947,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16967,12 +16967,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16982,13 +16982,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>418.63</v>
+        <v>719.25</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1574-80-CM26</t>
+          <t>548238-80-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17008,17 +17008,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17043,13 +17043,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>43.84</v>
+        <v>1222.91</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4036-271-CM26</t>
+          <t>1079505-271-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17104,13 +17104,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>731.61</v>
+        <v>411.55</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>548238-80-CM26</t>
+          <t>1574-80-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17130,17 +17130,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1243.92</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>383.59</v>
+        <v>378.14</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>292.64</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>324.84</v>
+        <v>322.82</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>186.78</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>221.17</v>
+        <v>222.18</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>193.18</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>134.05</v>
+        <v>136.04</v>
       </c>
     </row>
     <row r="282">
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>116.1</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1057440-325-CM26</t>
+          <t>3000-694-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17679,17 +17679,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17699,12 +17699,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17714,13 +17714,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1424.76</v>
+        <v>477.8</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1079505-318-CM26</t>
+          <t>1346282-285-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17740,17 +17740,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17775,13 +17775,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>143.5</v>
+        <v>341.48</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1346282-285-CM26</t>
+          <t>1057440-325-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17806,12 +17806,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17836,13 +17836,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>335.11</v>
+        <v>1451.84</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3000-694-CM26</t>
+          <t>1079505-318-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17867,12 +17867,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17882,12 +17882,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>468.88</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>311.09</v>
+        <v>313.24</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>223.41</v>
+        <v>224.95</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>177.72</v>
+        <v>178.95</v>
       </c>
     </row>
     <row r="290">
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>180.2</v>
+        <v>180.76</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3267-152-CM26</t>
+          <t>1962-363-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18172,12 +18172,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>438.31</v>
+        <v>769.01</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3267-153-CM26</t>
+          <t>3267-152-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18263,13 +18263,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>365.26</v>
+        <v>437.15</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1962-362-CM26</t>
+          <t>3267-153-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18309,12 +18309,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18324,13 +18324,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>915.9</v>
+        <v>364.29</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1962-363-CM26</t>
+          <t>1962-362-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>771.05</v>
+        <v>913.47</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>361.83</v>
+        <v>360.87</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1624.19</v>
+        <v>1602.56</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>5453.49</v>
+        <v>5380.85</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2155.05</v>
+        <v>2126.35</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>163.6</v>
+        <v>160.4</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>63959.61</v>
+        <v>62645.13</v>
       </c>
     </row>
     <row r="301">
@@ -18812,13 +18812,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>609.9</v>
+        <v>597.36</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3532-99-CM26</t>
+          <t>2996-140-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18843,12 +18843,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18858,12 +18858,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -18873,13 +18873,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1606.74</v>
+        <v>1192.1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2996-140-CM26</t>
+          <t>3712-470-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18904,12 +18904,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18934,13 +18934,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1180.88</v>
+        <v>1204.07</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3712-470-CM26</t>
+          <t>3532-99-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18965,12 +18965,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18980,12 +18980,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1192.74</v>
+        <v>1622.01</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>482.02</v>
+        <v>483.9</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>173.79</v>
+        <v>174.47</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>47.13</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>602.8200000000001</v>
+        <v>605.17</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>991.91</v>
+        <v>1001.89</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>190.89</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1004.69</v>
+        <v>1014.75</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5023.47</v>
+        <v>5049.07</v>
       </c>
     </row>
     <row r="313">
@@ -19544,13 +19544,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>595.15</v>
+        <v>598.1799999999999</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3712-465-CM26</t>
+          <t>1079505-373-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19575,12 +19575,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19590,12 +19590,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19605,13 +19605,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>6382.72</v>
+        <v>2069.42</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1079505-373-CM26</t>
+          <t>3712-465-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19636,12 +19636,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19651,12 +19651,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2058.93</v>
+        <v>6415.25</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>301.41</v>
+        <v>302.94</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>818.33</v>
+        <v>814.1799999999999</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>79.34999999999999</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>5525.82</v>
+        <v>5497.83</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>236.99</v>
+        <v>235.78</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1988.94</v>
+        <v>1993.5</v>
       </c>
     </row>
     <row r="322">
@@ -20093,13 +20093,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>89.5</v>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2448-705-CM26</t>
+          <t>1079505-388-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20119,17 +20119,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20154,13 +20154,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>595.15</v>
+        <v>348.86</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3687-191-CM26</t>
+          <t>2448-705-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20180,17 +20180,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20200,12 +20200,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20215,13 +20215,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>68.63</v>
+        <v>596.51</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1079505-388-CM26</t>
+          <t>3687-191-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20246,12 +20246,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20261,12 +20261,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>348.06</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>262.43</v>
+        <v>264.19</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1309.43</v>
+        <v>1318.19</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5036.25</v>
+        <v>5071.5</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>162.13</v>
+        <v>161.77</v>
       </c>
     </row>
     <row r="330">
@@ -20581,13 +20581,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>367.95</v>
+        <v>367.22</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1079505-417-CM26</t>
+          <t>2147-340-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20612,12 +20612,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20627,12 +20627,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -20642,13 +20642,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>323.2</v>
+        <v>1522.05</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2147-340-CM26</t>
+          <t>1079505-417-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20673,12 +20673,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20688,12 +20688,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1530.91</v>
+        <v>321.33</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>908.83</v>
+        <v>894.16</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>906.53</v>
+        <v>891.9</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1988.94</v>
+        <v>1957.05</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>99.45</v>
+        <v>97.84999999999999</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>100.98</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>419.95</v>
+        <v>413.21</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>201.96</v>
+        <v>199.61</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1767.16</v>
+        <v>1746.6</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>270.26</v>
+        <v>268.76</v>
       </c>
     </row>
     <row r="342">
@@ -21313,13 +21313,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1636.65</v>
+        <v>1628.61</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1079505-442-CM26</t>
+          <t>707418-107-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21344,12 +21344,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21359,12 +21359,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21374,13 +21374,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>101.49</v>
+        <v>115.36</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>707418-107-CM26</t>
+          <t>1079505-442-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21405,12 +21405,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21420,12 +21420,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21435,7 +21435,190 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>114.59</v>
+        <v>102.17</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1346282-340-CM26</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>314.87</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1461054-308-CM26</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>72.83</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1057440-449-CM26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>1251.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/coquimbo.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M934"/>
+  <dimension ref="A1:M937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23719,7 +23719,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1057438-222-CM25</t>
+          <t>1430710-1880-CM25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1928.54</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1430710-1880-CM25</t>
+          <t>1057438-222-CM25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23824,17 +23824,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>124.39</v>
+        <v>1928.54</v>
       </c>
     </row>
     <row r="361">
@@ -27684,7 +27684,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2125-3997-CM25</t>
+          <t>1574-368-CM25</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27724,17 +27724,17 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4642.44</v>
+        <v>108.82</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1574-368-CM25</t>
+          <t>2125-3997-CM25</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27789,17 +27789,17 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -27808,7 +27808,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>108.82</v>
+        <v>4642.44</v>
       </c>
     </row>
     <row r="422">
@@ -35289,7 +35289,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>1079505-8-CM26</t>
+          <t>1079505-6-CM26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -35348,13 +35348,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>116.77</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1079505-6-CM26</t>
+          <t>1079505-5-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35413,13 +35413,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>124.24</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1079505-5-CM26</t>
+          <t>1079505-4-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35478,13 +35478,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>109.29</v>
+        <v>186.83</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>1079505-4-CM26</t>
+          <t>1079505-2-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35543,13 +35543,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>186.83</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1079505-2-CM26</t>
+          <t>1079505-8-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35874,7 +35874,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2125-78-CM26</t>
+          <t>4036-15-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35894,17 +35894,17 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35914,17 +35914,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>5246.58</v>
+        <v>7288.67</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>4036-15-CM26</t>
+          <t>2125-78-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35959,17 +35959,17 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35979,17 +35979,17 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>7288.67</v>
+        <v>5246.58</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1057440-10-CM26</t>
+          <t>1962-17-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36029,12 +36029,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -36044,17 +36044,17 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
@@ -36063,13 +36063,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1194.77</v>
+        <v>848.12</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>1962-17-CM26</t>
+          <t>1057440-10-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -36094,12 +36094,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -36109,17 +36109,17 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -36128,7 +36128,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>848.12</v>
+        <v>1194.77</v>
       </c>
     </row>
     <row r="550">
@@ -36589,7 +36589,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>539119-249-CM26</t>
+          <t>539119-12-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36648,13 +36648,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1190.38</v>
+        <v>582.97</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>539119-12-CM26</t>
+          <t>539119-249-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36713,7 +36713,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>582.97</v>
+        <v>1190.38</v>
       </c>
     </row>
     <row r="559">
@@ -37239,7 +37239,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>627786-18-CM26</t>
+          <t>3276-9433-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -37264,12 +37264,12 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -37279,17 +37279,17 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -37298,13 +37298,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1419.58</v>
+        <v>688.4299999999999</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>3276-9433-CM26</t>
+          <t>627786-18-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37329,12 +37329,12 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -37344,17 +37344,17 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
@@ -37363,13 +37363,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>688.4299999999999</v>
+        <v>1419.58</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>1079505-34-CM26</t>
+          <t>1430710-95-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37394,12 +37394,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -37409,17 +37409,17 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
@@ -37428,13 +37428,13 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>279.94</v>
+        <v>289.26</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2146-35-CM26</t>
+          <t>1079505-35-CM26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -37459,12 +37459,12 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -37474,17 +37474,17 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -37493,13 +37493,13 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>394.7</v>
+        <v>326.6</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1079505-35-CM26</t>
+          <t>1079505-34-CM26</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -37558,13 +37558,13 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>326.6</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1079505-36-CM26</t>
+          <t>2146-35-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -37589,12 +37589,12 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -37623,13 +37623,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>1973.5</v>
+        <v>394.7</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1430710-95-CM26</t>
+          <t>1079505-36-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37654,12 +37654,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -37688,7 +37688,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>289.26</v>
+        <v>1973.5</v>
       </c>
     </row>
     <row r="574">
@@ -37824,7 +37824,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>539119-352-CM26</t>
+          <t>3182-15-CM26</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37849,12 +37849,12 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.102.073-2</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -37864,17 +37864,17 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
@@ -37883,13 +37883,13 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>952.84</v>
+        <v>3538.95</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>3182-15-CM26</t>
+          <t>539119-352-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>61.102.073-2</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37929,17 +37929,17 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K577" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
@@ -37948,13 +37948,13 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>3538.95</v>
+        <v>952.84</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>3688-43-CM26</t>
+          <t>1242121-73-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37974,17 +37974,17 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -37994,17 +37994,17 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
@@ -38013,13 +38013,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>79.97</v>
+        <v>4684.6</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1242121-73-CM26</t>
+          <t>3688-43-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -38039,17 +38039,17 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -38059,17 +38059,17 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -38078,7 +38078,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>4684.6</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="580">
@@ -38149,7 +38149,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>3000-187-CM26</t>
+          <t>2555-23-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -38174,12 +38174,12 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -38189,17 +38189,17 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>260.1</v>
+        <v>139.14</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2555-23-CM26</t>
+          <t>3000-187-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -38239,12 +38239,12 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -38254,17 +38254,17 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
@@ -38273,7 +38273,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>139.14</v>
+        <v>260.1</v>
       </c>
     </row>
     <row r="583">
@@ -39644,7 +39644,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>3182-22-CM26</t>
+          <t>1079505-59-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -39669,12 +39669,12 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>61.102.073-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -39684,17 +39684,17 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -39703,13 +39703,13 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>1120.21</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1079505-59-CM26</t>
+          <t>3182-22-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39734,12 +39734,12 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.102.073-2</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -39749,17 +39749,17 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
@@ -39768,7 +39768,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>81.12</v>
+        <v>1120.21</v>
       </c>
     </row>
     <row r="606">
@@ -40099,7 +40099,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1079505-66-CM26</t>
+          <t>1079505-68-CM26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>238.68</v>
+        <v>260.38</v>
       </c>
     </row>
     <row r="612">
@@ -40424,7 +40424,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>1079505-68-CM26</t>
+          <t>1079505-66-CM26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -40483,7 +40483,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>260.38</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="617">
@@ -40684,7 +40684,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>3712-205-CM26</t>
+          <t>3712-206-CM26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -40724,17 +40724,17 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -40743,13 +40743,13 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1606.76</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>3712-206-CM26</t>
+          <t>3511-61-CM26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -40769,17 +40769,17 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -40789,17 +40789,17 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -40808,13 +40808,13 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1333.09</v>
+        <v>250.64</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>3511-61-CM26</t>
+          <t>1079505-79-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -40834,17 +40834,17 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -40854,17 +40854,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>250.64</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>1079505-79-CM26</t>
+          <t>3712-205-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -40904,12 +40904,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -40919,17 +40919,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -40938,7 +40938,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>407.9</v>
+        <v>1606.76</v>
       </c>
     </row>
     <row r="624">
@@ -41529,7 +41529,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2711-65-CM26</t>
+          <t>1430710-159-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -41549,17 +41549,17 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -41569,17 +41569,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -41588,7 +41588,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>752.52</v>
+        <v>243.17</v>
       </c>
     </row>
     <row r="634">
@@ -41724,7 +41724,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>1430710-159-CM26</t>
+          <t>2711-65-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -41744,17 +41744,17 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -41764,17 +41764,17 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -41783,7 +41783,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>243.17</v>
+        <v>752.52</v>
       </c>
     </row>
     <row r="637">
@@ -42049,7 +42049,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>1574-41-CM26</t>
+          <t>1574-42-CM26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -42108,13 +42108,13 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>6090.86</v>
+        <v>1182.16</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>1574-42-CM26</t>
+          <t>1574-41-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -42173,13 +42173,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1182.16</v>
+        <v>6090.86</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>1962-146-CM26</t>
+          <t>2450-318-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42204,12 +42204,12 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -42219,17 +42219,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -42238,7 +42238,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>554.74</v>
+        <v>32810.13</v>
       </c>
     </row>
     <row r="644">
@@ -42309,7 +42309,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2450-318-CM26</t>
+          <t>1962-146-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42334,12 +42334,12 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -42349,17 +42349,17 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -42368,7 +42368,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>32810.13</v>
+        <v>554.74</v>
       </c>
     </row>
     <row r="646">
@@ -42439,7 +42439,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1797-21-CM26</t>
+          <t>1346282-128-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42464,12 +42464,12 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -42479,17 +42479,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -42498,13 +42498,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>1065.69</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>1346282-128-CM26</t>
+          <t>1797-21-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42529,12 +42529,12 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -42544,17 +42544,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -42563,13 +42563,13 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>68.64</v>
+        <v>1065.69</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>627786-61-CM26</t>
+          <t>1962-156-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42594,12 +42594,12 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -42628,13 +42628,13 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>358.32</v>
+        <v>808.52</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>548238-21-CM26</t>
+          <t>627786-61-CM26</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -42659,12 +42659,12 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -42674,17 +42674,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -42693,13 +42693,13 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>1031.88</v>
+        <v>358.32</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>548238-22-CM26</t>
+          <t>548238-21-CM26</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -42758,13 +42758,13 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>205.01</v>
+        <v>1031.88</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>1962-156-CM26</t>
+          <t>548238-22-CM26</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -42784,17 +42784,17 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -42804,17 +42804,17 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
@@ -42823,7 +42823,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>808.52</v>
+        <v>205.01</v>
       </c>
     </row>
     <row r="653">
@@ -43154,7 +43154,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2992-89-CM26</t>
+          <t>1242121-175-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -43179,12 +43179,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -43213,13 +43213,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>170.56</v>
+        <v>274.45</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>1242121-175-CM26</t>
+          <t>2992-89-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -43244,12 +43244,12 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -43278,7 +43278,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>274.45</v>
+        <v>170.56</v>
       </c>
     </row>
     <row r="660">
@@ -43414,7 +43414,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>3616-41-CM26</t>
+          <t>2125-799-CM26</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -43439,12 +43439,12 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -43454,17 +43454,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -43473,13 +43473,13 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>684.63</v>
+        <v>6375.5</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2125-799-CM26</t>
+          <t>3616-41-CM26</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -43504,12 +43504,12 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -43519,17 +43519,17 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -43538,7 +43538,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>6375.5</v>
+        <v>684.63</v>
       </c>
     </row>
     <row r="664">
@@ -43609,7 +43609,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>1079505-142-CM26</t>
+          <t>1242121-182-CM26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -43634,12 +43634,12 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -43649,17 +43649,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
@@ -43668,13 +43668,13 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>1160.33</v>
+        <v>5801.67</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>1242121-182-CM26</t>
+          <t>1229-14-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -43699,12 +43699,12 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>60.804.006-4</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -43714,17 +43714,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -43733,13 +43733,13 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>5801.67</v>
+        <v>836.64</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>1229-14-CM26</t>
+          <t>1079505-142-CM26</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -43764,12 +43764,12 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>60.804.006-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -43798,13 +43798,13 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>836.64</v>
+        <v>1160.33</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>1079505-158-CM26</t>
+          <t>1079505-157-CM26</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -43869,7 +43869,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>1079505-157-CM26</t>
+          <t>1079505-158-CM26</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -43934,7 +43934,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>1057440-223-CM26</t>
+          <t>1079505-159-CM26</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -43959,12 +43959,12 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -43974,17 +43974,17 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L670" t="inlineStr">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>1495.7</v>
+        <v>93.81</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>3509-139-CM26</t>
+          <t>1057440-223-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -44019,17 +44019,17 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -44039,17 +44039,17 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -44058,13 +44058,13 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>1942.82</v>
+        <v>1495.7</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>1079505-159-CM26</t>
+          <t>3509-139-CM26</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -44084,17 +44084,17 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -44104,17 +44104,17 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L672" t="inlineStr">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>93.81</v>
+        <v>1942.82</v>
       </c>
     </row>
     <row r="673">
@@ -44714,7 +44714,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>548238-54-CM26</t>
+          <t>3712-317-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -44739,12 +44739,12 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -44754,17 +44754,17 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
@@ -44773,13 +44773,13 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>178.07</v>
+        <v>1113.2</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>3712-317-CM26</t>
+          <t>1660-316-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -44804,12 +44804,12 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -44838,13 +44838,13 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1113.2</v>
+        <v>844.24</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>1660-316-CM26</t>
+          <t>1962-211-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44869,12 +44869,12 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -44884,17 +44884,17 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L684" t="inlineStr">
@@ -44903,7 +44903,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>844.24</v>
+        <v>446.24</v>
       </c>
     </row>
     <row r="685">
@@ -44974,7 +44974,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>1962-211-CM26</t>
+          <t>548238-54-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44999,12 +44999,12 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -45014,17 +45014,17 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -45033,13 +45033,13 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>446.24</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>627786-81-CM26</t>
+          <t>3267-63-CM26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -45064,12 +45064,12 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -45079,17 +45079,17 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
@@ -45098,13 +45098,13 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>2222.28</v>
+        <v>432.32</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>3267-63-CM26</t>
+          <t>1962-223-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -45129,12 +45129,12 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -45144,17 +45144,17 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
@@ -45163,7 +45163,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>432.32</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="689">
@@ -45234,7 +45234,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>1962-223-CM26</t>
+          <t>627786-81-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -45259,12 +45259,12 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -45293,7 +45293,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>928.76</v>
+        <v>2222.28</v>
       </c>
     </row>
     <row r="691">
@@ -45429,7 +45429,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>1250339-12-CM26</t>
+          <t>2555-69-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -45454,12 +45454,12 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -45469,17 +45469,17 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
@@ -45488,13 +45488,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>218.86</v>
+        <v>168.77</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2555-69-CM26</t>
+          <t>1250339-12-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -45519,12 +45519,12 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -45534,17 +45534,17 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -45553,13 +45553,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>168.77</v>
+        <v>218.86</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>3000-545-CM26</t>
+          <t>3182-68-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -45579,17 +45579,17 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.102.073-2</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -45599,17 +45599,17 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -45618,13 +45618,13 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>274.3</v>
+        <v>342.27</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>3182-68-CM26</t>
+          <t>3000-545-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -45644,17 +45644,17 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>61.102.073-2</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -45664,17 +45664,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -45683,13 +45683,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>342.27</v>
+        <v>274.3</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>1079505-204-CM26</t>
+          <t>1079505-202-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -45729,17 +45729,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -45748,7 +45748,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>516.37</v>
+        <v>340.23</v>
       </c>
     </row>
     <row r="698">
@@ -45819,7 +45819,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>1079505-195-CM26</t>
+          <t>1079505-201-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45878,13 +45878,13 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>110.57</v>
+        <v>141.76</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>1079505-200-CM26</t>
+          <t>1079505-195-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -45943,13 +45943,13 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>396.93</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>3615-67-CM26</t>
+          <t>1079505-200-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45974,12 +45974,12 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -45989,17 +45989,17 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
@@ -46008,7 +46008,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>376.42</v>
+        <v>396.93</v>
       </c>
     </row>
     <row r="702">
@@ -46079,7 +46079,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>1079505-202-CM26</t>
+          <t>3615-67-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -46104,12 +46104,12 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -46119,17 +46119,17 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
@@ -46138,13 +46138,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>340.23</v>
+        <v>376.42</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>1079505-201-CM26</t>
+          <t>1079505-204-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -46184,17 +46184,17 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L704" t="inlineStr">
@@ -46203,7 +46203,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>141.76</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="705">
@@ -46664,7 +46664,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>1323-5-CM26</t>
+          <t>1057440-275-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46684,17 +46684,17 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -46704,17 +46704,17 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -46723,13 +46723,13 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>146.56</v>
+        <v>1583.46</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1079505-213-CM26</t>
+          <t>1323-5-CM26</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -46749,17 +46749,17 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -46769,17 +46769,17 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -46788,13 +46788,13 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>111.31</v>
+        <v>146.56</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>1057440-275-CM26</t>
+          <t>1079505-213-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -46819,12 +46819,12 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -46834,17 +46834,17 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -46853,7 +46853,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>1583.46</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="715">
@@ -47119,7 +47119,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>1886-13-CM26</t>
+          <t>1057439-3641-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -47144,12 +47144,12 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -47159,17 +47159,17 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
@@ -47178,13 +47178,13 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>3416.88</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>1057439-3641-CM26</t>
+          <t>1346282-230-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47209,12 +47209,12 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -47224,17 +47224,17 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
@@ -47243,7 +47243,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3416.88</v>
+        <v>1354.84</v>
       </c>
     </row>
     <row r="721">
@@ -47314,7 +47314,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>1346282-230-CM26</t>
+          <t>1886-13-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -47339,12 +47339,12 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -47354,17 +47354,17 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -47373,7 +47373,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>1354.84</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="723">
@@ -47509,7 +47509,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2711-132-CM26</t>
+          <t>1962-292-CM26</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -47529,17 +47529,17 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -47549,17 +47549,17 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
@@ -47568,13 +47568,13 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>2367.97</v>
+        <v>734.08</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>1079505-260-CM26</t>
+          <t>2711-132-CM26</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -47594,17 +47594,17 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -47614,17 +47614,17 @@
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
@@ -47633,7 +47633,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>181.52</v>
+        <v>2367.97</v>
       </c>
     </row>
     <row r="727">
@@ -47704,7 +47704,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>1962-292-CM26</t>
+          <t>1079505-260-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47729,12 +47729,12 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -47744,17 +47744,17 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
@@ -47763,7 +47763,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>734.08</v>
+        <v>181.52</v>
       </c>
     </row>
     <row r="729">
@@ -48159,7 +48159,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>1984-10-CM26</t>
+          <t>1079505-275-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -48184,12 +48184,12 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>60.701.009-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -48199,17 +48199,17 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
@@ -48218,13 +48218,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>156.46</v>
+        <v>217.48</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>1079505-275-CM26</t>
+          <t>707418-74-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48249,12 +48249,12 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -48264,17 +48264,17 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
@@ -48283,13 +48283,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>217.48</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>707418-74-CM26</t>
+          <t>707418-75-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -48329,17 +48329,17 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
@@ -48348,13 +48348,13 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>122.16</v>
+        <v>99.53</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>707418-75-CM26</t>
+          <t>707418-77-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -48394,17 +48394,17 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
@@ -48413,13 +48413,13 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>99.53</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>707418-76-CM26</t>
+          <t>707418-78-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -48484,7 +48484,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>707418-78-CM26</t>
+          <t>3511-220-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -48504,17 +48504,17 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -48524,17 +48524,17 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
@@ -48543,13 +48543,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>122.16</v>
+        <v>157.62</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>3511-220-CM26</t>
+          <t>1984-10-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -48569,17 +48569,17 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.701.009-9</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -48589,17 +48589,17 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -48608,13 +48608,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>157.62</v>
+        <v>156.46</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>707418-77-CM26</t>
+          <t>707418-76-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48939,7 +48939,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>4036-271-CM26</t>
+          <t>1574-80-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48959,17 +48959,17 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -48979,17 +48979,17 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
@@ -48998,13 +48998,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>719.25</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>548238-80-CM26</t>
+          <t>4036-271-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -49024,17 +49024,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -49044,17 +49044,17 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
@@ -49063,13 +49063,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>1222.91</v>
+        <v>719.25</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>1574-80-CM26</t>
+          <t>548238-80-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -49094,12 +49094,12 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -49128,7 +49128,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>43.1</v>
+        <v>1222.91</v>
       </c>
     </row>
     <row r="750">
@@ -49394,7 +49394,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>1079505-295-CM26</t>
+          <t>1079505-294-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -49453,13 +49453,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>185.62</v>
+        <v>322.82</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>1079505-294-CM26</t>
+          <t>1079505-295-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49518,7 +49518,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>322.82</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="756">
@@ -50044,7 +50044,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>1159-159-CM26</t>
+          <t>548854-28-CM26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -50069,12 +50069,12 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -50084,17 +50084,17 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L764" t="inlineStr">
@@ -50103,13 +50103,13 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>178.95</v>
+        <v>313.24</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>548854-28-CM26</t>
+          <t>1159-159-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -50134,12 +50134,12 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -50149,17 +50149,17 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L765" t="inlineStr">
@@ -50168,7 +50168,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>313.24</v>
+        <v>178.95</v>
       </c>
     </row>
     <row r="766">
@@ -50304,7 +50304,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>1962-362-CM26</t>
+          <t>3267-153-CM26</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -50329,12 +50329,12 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -50344,17 +50344,17 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
@@ -50363,13 +50363,13 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>913.47</v>
+        <v>364.29</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>1962-363-CM26</t>
+          <t>1962-362-CM26</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -50409,17 +50409,17 @@
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L769" t="inlineStr">
@@ -50428,13 +50428,13 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>769.01</v>
+        <v>913.47</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>1962-366-CM26</t>
+          <t>1962-363-CM26</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
@@ -50474,17 +50474,17 @@
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L770" t="inlineStr">
@@ -50493,13 +50493,13 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>360.87</v>
+        <v>769.01</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>3267-152-CM26</t>
+          <t>1962-366-CM26</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -50519,17 +50519,17 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -50539,17 +50539,17 @@
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L771" t="inlineStr">
@@ -50558,13 +50558,13 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>437.15</v>
+        <v>360.87</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>3267-153-CM26</t>
+          <t>3267-152-CM26</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -50623,7 +50623,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>364.29</v>
+        <v>437.15</v>
       </c>
     </row>
     <row r="773">
@@ -50889,7 +50889,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>1079505-247-CM26</t>
+          <t>4295-62-CM26</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -50909,17 +50909,17 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -50929,17 +50929,17 @@
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
@@ -50948,13 +50948,13 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>597.36</v>
+        <v>62645.13</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>4295-62-CM26</t>
+          <t>1079505-247-CM26</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -50974,17 +50974,17 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -50994,17 +50994,17 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
@@ -51013,7 +51013,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>62645.13</v>
+        <v>597.36</v>
       </c>
     </row>
     <row r="779">
@@ -51214,7 +51214,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>1079505-355-CM26</t>
+          <t>2552-12-CM26</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -51239,12 +51239,12 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -51254,17 +51254,17 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
@@ -51273,13 +51273,13 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>483.9</v>
+        <v>174.47</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2552-12-CM26</t>
+          <t>1230663-134-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -51304,12 +51304,12 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.100.165-k</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -51338,13 +51338,13 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>174.47</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>1230663-134-CM26</t>
+          <t>1962-384-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -51369,12 +51369,12 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>65.100.165-k</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -51384,17 +51384,17 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
@@ -51403,13 +51403,13 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>47.31</v>
+        <v>605.17</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>1962-384-CM26</t>
+          <t>1079505-355-CM26</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -51434,12 +51434,12 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -51468,7 +51468,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>605.17</v>
+        <v>483.9</v>
       </c>
     </row>
     <row r="786">
@@ -51539,7 +51539,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2145-600-CM26</t>
+          <t>2992-242-CM26</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -51564,12 +51564,12 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -51598,13 +51598,13 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>1014.75</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2992-242-CM26</t>
+          <t>2145-600-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -51629,12 +51629,12 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -51663,13 +51663,13 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>192.8</v>
+        <v>1014.75</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>1079505-373-CM26</t>
+          <t>3712-465-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -51694,12 +51694,12 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -51709,17 +51709,17 @@
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L789" t="inlineStr">
@@ -51728,13 +51728,13 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>2069.42</v>
+        <v>6415.25</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>3182-108-CM26</t>
+          <t>1079505-373-CM26</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -51759,12 +51759,12 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>61.102.073-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -51774,17 +51774,17 @@
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L790" t="inlineStr">
@@ -51793,13 +51793,13 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>302.94</v>
+        <v>2069.42</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>1079505-376-CM26</t>
+          <t>3182-108-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51824,12 +51824,12 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.102.073-2</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -51839,17 +51839,17 @@
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>598.1799999999999</v>
+        <v>302.94</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>1242121-348-CM26</t>
+          <t>1079505-376-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51889,12 +51889,12 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -51904,17 +51904,17 @@
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
@@ -51923,13 +51923,13 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>5049.07</v>
+        <v>598.1799999999999</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>3712-465-CM26</t>
+          <t>1242121-348-CM26</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -51954,12 +51954,12 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -51988,7 +51988,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>6415.25</v>
+        <v>5049.07</v>
       </c>
     </row>
     <row r="794">
@@ -52254,7 +52254,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>1660-614-CM26</t>
+          <t>3687-191-CM26</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -52274,17 +52274,17 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
@@ -52294,17 +52294,17 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L798" t="inlineStr">
@@ -52313,13 +52313,13 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>1993.5</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>3687-191-CM26</t>
+          <t>2448-705-CM26</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -52339,17 +52339,17 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
@@ -52359,17 +52359,17 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L799" t="inlineStr">
@@ -52378,13 +52378,13 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>68.79000000000001</v>
+        <v>596.51</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2448-705-CM26</t>
+          <t>1079505-388-CM26</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -52409,12 +52409,12 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
@@ -52443,13 +52443,13 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>596.51</v>
+        <v>348.86</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>1079505-388-CM26</t>
+          <t>1079505-391-CM26</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -52508,13 +52508,13 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>348.86</v>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>1079505-391-CM26</t>
+          <t>1660-614-CM26</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -52539,12 +52539,12 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -52573,7 +52573,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>89.70999999999999</v>
+        <v>1993.5</v>
       </c>
     </row>
     <row r="803">
@@ -53164,7 +53164,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2146-380-CM26</t>
+          <t>707418-101-CM26</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -53189,12 +53189,12 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -53204,17 +53204,17 @@
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
@@ -53223,13 +53223,13 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>413.21</v>
+        <v>97.84999999999999</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>707418-101-CM26</t>
+          <t>707418-102-CM26</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -53288,13 +53288,13 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>97.84999999999999</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>707418-102-CM26</t>
+          <t>2146-380-CM26</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -53319,12 +53319,12 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -53334,17 +53334,17 @@
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L814" t="inlineStr">
@@ -53353,7 +53353,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>99.36</v>
+        <v>413.21</v>
       </c>
     </row>
     <row r="815">
@@ -53424,7 +53424,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>3750-182-CM26</t>
+          <t>1079505-419-CM26</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -53444,17 +53444,17 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -53483,13 +53483,13 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>1746.6</v>
+        <v>199.61</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>1079505-419-CM26</t>
+          <t>3750-182-CM26</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -53509,17 +53509,17 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
@@ -53548,7 +53548,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>199.61</v>
+        <v>1746.6</v>
       </c>
     </row>
     <row r="818">
@@ -53944,7 +53944,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>1962-500-CM26</t>
+          <t>1159-210-CM26</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -53969,12 +53969,12 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -53984,17 +53984,17 @@
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
@@ -54003,13 +54003,13 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>620.67</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>1159-210-CM26</t>
+          <t>1962-500-CM26</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -54034,12 +54034,12 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -54049,17 +54049,17 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
@@ -54068,7 +54068,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>85.75</v>
+        <v>620.67</v>
       </c>
     </row>
     <row r="826">
@@ -54269,7 +54269,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>539119-2508-CM26</t>
+          <t>1079505-461-CM26</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -54294,7 +54294,7 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
@@ -54309,17 +54309,17 @@
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
@@ -54328,13 +54328,13 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>1023.39</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>1079505-461-CM26</t>
+          <t>2446-894-CM26</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -54359,12 +54359,12 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -54374,17 +54374,17 @@
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
@@ -54393,13 +54393,13 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>103.38</v>
+        <v>86426.55</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2446-894-CM26</t>
+          <t>539119-2508-CM26</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -54424,12 +54424,12 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -54439,17 +54439,17 @@
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K831" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L831" t="inlineStr">
@@ -54458,7 +54458,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>86426.55</v>
+        <v>1023.39</v>
       </c>
     </row>
     <row r="832">
@@ -55439,7 +55439,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>1079505-507-CM26</t>
+          <t>1079505-505-CM26</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -55479,17 +55479,17 @@
       </c>
       <c r="I847" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K847" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
@@ -55498,7 +55498,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>437.13</v>
+        <v>287.5</v>
       </c>
     </row>
     <row r="848">
@@ -55569,7 +55569,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>1079505-505-CM26</t>
+          <t>1079505-507-CM26</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -55609,17 +55609,17 @@
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
@@ -55628,7 +55628,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>287.5</v>
+        <v>437.13</v>
       </c>
     </row>
     <row r="850">
@@ -55829,7 +55829,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>1057439-5635-CM26</t>
+          <t>1962-570-CM26</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -55854,12 +55854,12 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -55869,17 +55869,17 @@
       </c>
       <c r="I853" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
@@ -55888,7 +55888,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>408.3</v>
+        <v>574.13</v>
       </c>
     </row>
     <row r="854">
@@ -55959,7 +55959,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>1962-570-CM26</t>
+          <t>1057439-5635-CM26</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -55984,12 +55984,12 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -55999,17 +55999,17 @@
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
@@ -56018,7 +56018,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>574.13</v>
+        <v>408.3</v>
       </c>
     </row>
     <row r="856">
@@ -56219,7 +56219,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>1079505-515-CM26</t>
+          <t>1079505-528-CM26</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -56278,13 +56278,13 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>69.92</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>1079505-516-CM26</t>
+          <t>1079505-515-CM26</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -56343,13 +56343,13 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>116.54</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>1079505-528-CM26</t>
+          <t>1242121-461-CM26</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -56374,12 +56374,12 @@
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -56389,17 +56389,17 @@
       </c>
       <c r="I861" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K861" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L861" t="inlineStr">
@@ -56408,13 +56408,13 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>74.59</v>
+        <v>4725.15</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>3614-268-CM26</t>
+          <t>1079505-516-CM26</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -56434,17 +56434,17 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -56473,13 +56473,13 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>466.16</v>
+        <v>116.54</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>1242121-461-CM26</t>
+          <t>3614-268-CM26</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -56499,17 +56499,17 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
@@ -56519,17 +56519,17 @@
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K863" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L863" t="inlineStr">
@@ -56538,7 +56538,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>4725.15</v>
+        <v>466.16</v>
       </c>
     </row>
     <row r="864">
@@ -56739,7 +56739,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>3753-252-CM26</t>
+          <t>1574-241-CM26</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -56759,17 +56759,17 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -56779,17 +56779,17 @@
       </c>
       <c r="I867" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K867" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L867" t="inlineStr">
@@ -56798,13 +56798,13 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>533.3</v>
+        <v>331.87</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>1574-241-CM26</t>
+          <t>3753-252-CM26</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -56824,17 +56824,17 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -56844,17 +56844,17 @@
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K868" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L868" t="inlineStr">
@@ -56863,7 +56863,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>331.87</v>
+        <v>533.3</v>
       </c>
     </row>
     <row r="869">
@@ -56999,7 +56999,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>707418-128-CM26</t>
+          <t>3000-926-CM26</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -57019,17 +57019,17 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
@@ -57039,17 +57039,17 @@
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K871" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L871" t="inlineStr">
@@ -57058,13 +57058,13 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>94.47</v>
+        <v>332.56</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>3000-926-CM26</t>
+          <t>707418-128-CM26</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -57084,17 +57084,17 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -57104,17 +57104,17 @@
       </c>
       <c r="I872" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K872" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L872" t="inlineStr">
@@ -57123,7 +57123,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>332.56</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="873">
@@ -57584,7 +57584,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>1079505-590-CM26</t>
+          <t>1079505-588-CM26</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -57643,7 +57643,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>139.08</v>
+        <v>324.53</v>
       </c>
     </row>
     <row r="881">
@@ -57714,7 +57714,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>1079505-588-CM26</t>
+          <t>1079505-590-CM26</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -57773,7 +57773,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>324.53</v>
+        <v>139.08</v>
       </c>
     </row>
     <row r="883">
@@ -58579,7 +58579,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
@@ -59229,7 +59229,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
@@ -59924,7 +59924,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>1079505-659-CM26</t>
+          <t>1079505-658-CM26</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -59964,17 +59964,17 @@
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K916" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L916" t="inlineStr">
@@ -59983,13 +59983,13 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>266.31</v>
+        <v>484.82</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>1079505-650-CM26</t>
+          <t>1079505-659-CM26</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -60048,13 +60048,13 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>147.09</v>
+        <v>266.31</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>1079505-658-CM26</t>
+          <t>1079505-650-CM26</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -60094,17 +60094,17 @@
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K918" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L918" t="inlineStr">
@@ -60113,7 +60113,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>484.82</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="919">
@@ -60509,7 +60509,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>3712-710-CM26</t>
+          <t>3712-711-CM26</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -60549,17 +60549,17 @@
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K925" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L925" t="inlineStr">
@@ -60568,13 +60568,13 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>264.17</v>
+        <v>278.36</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>2446-1138-CM26</t>
+          <t>548238-161-CM26</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -60599,12 +60599,12 @@
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
@@ -60614,17 +60614,17 @@
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K926" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L926" t="inlineStr">
@@ -60633,13 +60633,13 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>73061.03999999999</v>
+        <v>128.89</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>3712-711-CM26</t>
+          <t>1962-695-CM26</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -60659,17 +60659,17 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
@@ -60698,13 +60698,13 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>278.36</v>
+        <v>955.73</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>539119-3324-CM26</t>
+          <t>3712-710-CM26</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -60724,17 +60724,17 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -60744,17 +60744,17 @@
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L928" t="inlineStr">
@@ -60763,13 +60763,13 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>644.4299999999999</v>
+        <v>264.17</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>1962-695-CM26</t>
+          <t>2446-1138-CM26</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -60789,17 +60789,17 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -60809,17 +60809,17 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L929" t="inlineStr">
@@ -60828,13 +60828,13 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>955.73</v>
+        <v>73061.03999999999</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>548238-161-CM26</t>
+          <t>539119-3324-CM26</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -60854,17 +60854,17 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
@@ -60893,7 +60893,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>128.89</v>
+        <v>644.4299999999999</v>
       </c>
     </row>
     <row r="931">
@@ -60919,7 +60919,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
@@ -60964,7 +60964,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>2125-2073-CM26</t>
+          <t>1057440-556-CM26</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -60989,12 +60989,12 @@
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -61023,13 +61023,13 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>5936.48</v>
+        <v>1403.17</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>3872-328-CM26</t>
+          <t>3714-301-CM26</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -61054,12 +61054,12 @@
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -61088,72 +61088,267 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>47.69</v>
+        <v>961.12</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
+          <t>3872-328-CM26</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>69.040.900-3</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M934" s="2" t="n">
+        <v>47.69</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2125-2073-CM26</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M935" s="2" t="n">
+        <v>5936.48</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
           <t>1079505-676-CM26</t>
         </is>
       </c>
-      <c r="B934" t="inlineStr">
-        <is>
-          <t>2239-1-LR25</t>
-        </is>
-      </c>
-      <c r="C934" t="inlineStr">
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D934" t="inlineStr">
+      <c r="D936" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E934" t="inlineStr">
+      <c r="E936" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F934" t="inlineStr">
+      <c r="F936" t="inlineStr">
         <is>
           <t>60.505.206-1</t>
         </is>
       </c>
-      <c r="G934" t="inlineStr">
+      <c r="G936" t="inlineStr">
         <is>
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H934" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I934" t="inlineStr">
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
         </is>
       </c>
-      <c r="J934" t="inlineStr">
+      <c r="J936" t="inlineStr">
         <is>
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr">
+      <c r="K936" t="inlineStr">
         <is>
           <t>Atacama</t>
         </is>
       </c>
-      <c r="L934" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M934" s="2" t="n">
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M936" s="2" t="n">
         <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>996-213-CM26</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M937" s="2" t="n">
+        <v>266.75</v>
       </c>
     </row>
   </sheetData>
